--- a/result_table.xlsx
+++ b/result_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Housing-Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D8AD867-AB7B-4242-9C9E-4B7687522BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499E0206-49E8-4058-AB92-A86492F7F94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{A1F1EF00-C3AB-4D9B-91EC-3DF2E2D3820D}"/>
   </bookViews>
@@ -125,12 +125,21 @@
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="2">
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -151,8 +160,8 @@
     <tableColumn id="2" xr3:uid="{FB8DD280-3656-45C3-B3CA-89D84BCE223E}" name="Scaling"/>
     <tableColumn id="3" xr3:uid="{13E2FC1D-A2E8-4A00-BD90-83F6756268DC}" name="Removing columns where #NaN &gt; 90%"/>
     <tableColumn id="4" xr3:uid="{7EB146EE-B238-4F48-ADE2-2BC2C2ECEB79}" name="RMSE"/>
-    <tableColumn id="5" xr3:uid="{7E6B41D6-390F-4A68-8071-3542213904BB}" name="Cross Validation mean"/>
-    <tableColumn id="6" xr3:uid="{916BF664-E7E0-4AF7-AE14-F752E747B846}" name="Cross Validation std"/>
+    <tableColumn id="5" xr3:uid="{7E6B41D6-390F-4A68-8071-3542213904BB}" name="Cross Validation mean" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{916BF664-E7E0-4AF7-AE14-F752E747B846}" name="Cross Validation std" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -480,8 +489,8 @@
   <cols>
     <col min="1" max="2" width="16.06640625" customWidth="1"/>
     <col min="3" max="3" width="32.33203125" customWidth="1"/>
-    <col min="5" max="5" width="20.73046875" customWidth="1"/>
-    <col min="6" max="6" width="19.86328125" customWidth="1"/>
+    <col min="5" max="5" width="20.73046875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="19.86328125" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.45">
@@ -497,10 +506,10 @@
       <c r="D1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
@@ -517,10 +526,10 @@
       <c r="D2">
         <v>29676.115000000002</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -537,10 +546,10 @@
       <c r="D3">
         <v>29833.273000000001</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>0.755</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>6.4000000000000001E-2</v>
       </c>
     </row>
@@ -557,10 +566,10 @@
       <c r="D4">
         <v>53684770188869.398</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -577,10 +586,10 @@
       <c r="D5">
         <v>29833.273000000001</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>0.80600000000000005</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>6.0999999999999999E-2</v>
       </c>
     </row>
@@ -597,10 +606,10 @@
       <c r="D6">
         <v>29837.517</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>0.80600000000000005</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>6.9000000000000006E-2</v>
       </c>
     </row>
@@ -617,10 +626,10 @@
       <c r="D7">
         <v>29359.474999999999</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>0.80400000000000005</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="G7" s="1" t="s">
@@ -659,7 +668,7 @@
       <c r="E8" s="2">
         <v>0.83499999999999996</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>5.0999999999999997E-2</v>
       </c>
     </row>
@@ -676,10 +685,10 @@
       <c r="D9">
         <v>29193.406999999999</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>0.84099999999999997</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>4.2999999999999997E-2</v>
       </c>
     </row>
@@ -696,10 +705,10 @@
       <c r="D10">
         <v>28223.554</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>0.84499999999999997</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>4.1000000000000002E-2</v>
       </c>
       <c r="G10" s="1" t="s">

--- a/result_table.xlsx
+++ b/result_table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Projects\Housing-Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{499E0206-49E8-4058-AB92-A86492F7F94A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75371CA8-C00C-4BA6-9F19-DB831124802A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="10965" windowHeight="12863" xr2:uid="{A1F1EF00-C3AB-4D9B-91EC-3DF2E2D3820D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A1F1EF00-C3AB-4D9B-91EC-3DF2E2D3820D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="17">
   <si>
     <t>Model</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>Comparing the Random Forrest model with the linear models, shows that a non-linear model estimates the prices a little better. Especially the RMSE value took a large drop when removing columns which almost only are nan</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>The Gradient Boosting is accuracy wise and RMSE wise the best estimator in the comparison. Esspially the relative low RMSE shows that this is probably the right model for this task.</t>
   </si>
 </sst>
 </file>
@@ -484,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55EA0821-4007-49C9-A091-297FB8C4C239}">
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="16.06640625" customWidth="1"/>
@@ -715,6 +721,69 @@
         <v>14</v>
       </c>
     </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>3</v>
+      </c>
+      <c r="C11" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11">
+        <v>27517.555</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="F11" s="2">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C12" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12">
+        <v>27159.332999999999</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="F12" s="2">
+        <v>5.1999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>2</v>
+      </c>
+      <c r="C13" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>26734.1</v>
+      </c>
+      <c r="E13" s="2">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="F13" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
